--- a/reports/jobs_2026-10-14.xlsx
+++ b/reports/jobs_2026-10-14.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CAD-DFT Engineer</t>
+          <t>GenAI-Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -538,11 +538,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -550,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/bengaluru/cad-dft-engineer/33099/98426141520</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -565,57 +561,57 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Expedia Group India</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer Czechia - Prague Technology</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>DevOps / SRE</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>https://careers.expediagroup.com/job/site-reliability-engineer/prague-prague/R-105042/</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Agnikul Cosmos</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>mailto:%20humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://agnikul.in/careers</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
+          <t>Chiang Mai 0 available jobs</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -628,7 +624,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 1 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -636,12 +636,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 0 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Mumbai 1 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 1 available jobs</t>
+          <t>Shanghai 2 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 2 available jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -812,11 +812,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -824,7 +820,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -846,7 +842,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -867,7 +863,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -889,7 +885,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
+          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -910,7 +906,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
+          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -932,7 +928,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -945,7 +941,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -953,7 +953,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -988,11 +988,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -1000,7 +996,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1022,12 +1018,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1043,7 +1039,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1065,12 +1061,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1086,7 +1082,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1103,12 +1099,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>CAD-DFT Engineer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1121,7 +1117,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careers.arm.com/job/bengaluru/cad-dft-engineer/33099/98426141520</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -2974,17 +2974,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/seattle-wa/R-110382-2/</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3017,17 +3017,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/san-jose-ca/R-110382-1/</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3060,17 +3060,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>AI Governance Arcitect</t>
+          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/austin-tx/R-110382/</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3103,17 +3103,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/austin-tx/R-110379/</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3146,17 +3146,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/san-jose-ca/R-110379-1/</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3189,12 +3189,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/seattle-wa/R-110379-2/</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3232,17 +3232,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/san-jose-ca/R-110306-1/</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3275,17 +3275,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3293,11 +3293,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3305,12 +3301,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/seattle-wa/R-110306-2/</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3322,17 +3318,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3340,11 +3336,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3352,12 +3344,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/austin-tx/R-110306/</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3369,17 +3361,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3387,11 +3379,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
       <c r="F65" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3399,12 +3387,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3416,12 +3404,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3434,11 +3422,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3446,12 +3430,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3463,17 +3447,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3481,11 +3465,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3493,12 +3473,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3510,17 +3490,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3536,12 +3516,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3553,17 +3533,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3579,12 +3559,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3596,12 +3576,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3614,11 +3594,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3626,12 +3602,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3643,17 +3619,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3663,7 +3639,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3673,12 +3649,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3690,17 +3666,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3708,7 +3684,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3716,12 +3696,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3733,12 +3713,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3753,7 +3733,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3763,12 +3743,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3780,17 +3760,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3798,7 +3778,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3806,12 +3790,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3823,17 +3807,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3843,7 +3827,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3853,12 +3837,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3870,17 +3854,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3888,11 +3872,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>India’s 100 th unicorn. C</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -3900,12 +3880,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers.html</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3917,17 +3897,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3943,12 +3923,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3960,17 +3940,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3980,7 +3960,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3990,12 +3970,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4007,17 +3987,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4037,12 +4017,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4054,17 +4034,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4072,11 +4052,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4084,12 +4060,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4101,17 +4077,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4121,7 +4097,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4131,12 +4107,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4148,17 +4124,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4166,11 +4142,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
       <c r="F82" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4178,12 +4150,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4195,17 +4167,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4213,7 +4185,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4221,12 +4197,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4238,17 +4214,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4258,7 +4234,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>India’s 100 th unicorn. C</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -4268,12 +4244,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://open.money/company/careers.html</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4285,17 +4261,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4303,11 +4279,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4315,12 +4287,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4332,17 +4304,17 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4352,7 +4324,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4362,12 +4334,12 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -4379,12 +4351,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4397,7 +4369,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4405,12 +4381,12 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4422,17 +4398,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4442,7 +4418,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -4452,12 +4428,12 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -4469,12 +4445,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4489,7 +4465,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -4499,12 +4475,12 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -4516,17 +4492,17 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4536,7 +4512,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -4546,12 +4522,12 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -4563,12 +4539,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -4581,11 +4557,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
       <c r="F91" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4593,12 +4565,12 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4610,27 +4582,27 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -4640,12 +4612,12 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -4657,17 +4629,17 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -4677,7 +4649,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -4687,12 +4659,12 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -4704,17 +4676,17 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -4724,7 +4696,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -4734,12 +4706,12 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -4751,29 +4723,25 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer- SaaS O365</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bangalore </t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4781,12 +4749,12 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -4798,17 +4766,17 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -4818,7 +4786,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -4828,12 +4796,12 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -4845,12 +4813,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4863,7 +4831,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4871,12 +4843,12 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -4888,12 +4860,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -4906,7 +4878,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4914,12 +4890,12 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -4931,12 +4907,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4949,7 +4925,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -4957,12 +4937,12 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -4974,12 +4954,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -4989,10 +4969,14 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr"/>
+          <t>0-2 years</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangalore </t>
+        </is>
+      </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -5000,12 +4984,12 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -5017,17 +5001,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5035,7 +5019,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -5043,12 +5031,12 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -5060,17 +5048,17 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5080,7 +5068,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -5090,12 +5078,12 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -5107,27 +5095,27 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Software Engineer- SaaS O365</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -5137,12 +5125,12 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -5154,17 +5142,17 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Intern- Employee Engagement</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5172,7 +5160,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -5180,12 +5172,12 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -5197,12 +5189,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -5223,12 +5215,12 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -5240,17 +5232,17 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -5258,11 +5250,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E106" s="4" t="inlineStr"/>
       <c r="F106" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -5270,12 +5258,12 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -5287,17 +5275,17 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Software Procurement Intern</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -5305,11 +5293,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Gurgaon, India; Pune, India</t>
-        </is>
-      </c>
+      <c r="E107" s="4" t="inlineStr"/>
       <c r="F107" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -5317,12 +5301,12 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5334,12 +5318,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5352,11 +5336,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -5364,12 +5344,12 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -5381,52 +5361,416 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>AI Animator</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>QA / SDET</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>SirionLabs</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Intern- Employee Engagement</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sirionlabs.com/careers/</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Sprinklr</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Internship and Early Careers</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Stripe India</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Software Procurement Intern</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Gurgaon, India; Pune, India</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I109" s="4" t="inlineStr">
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I109"/>
+  <autoFilter ref="A1:I117"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5536,6 +5880,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5595,15 +5947,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>INDmoney</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.indmoney.com/careers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5612,18 +5984,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5632,18 +6004,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5652,18 +6024,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5672,18 +6044,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5692,18 +6064,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5712,18 +6084,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Cleartrip</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5732,18 +6104,38 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Darwinbox</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://darwinbox.com/careers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -5752,18 +6144,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5772,18 +6164,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5792,38 +6184,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -5832,26 +6204,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Tata 1mg</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.1mg.com/jobs</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.1mg.com/jobs", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
